--- a/branches/migration/2026.0.0-template-v0.13.2/all-profiles.xlsx
+++ b/branches/migration/2026.0.0-template-v0.13.2/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.0</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
